--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -2395,48 +2395,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>98347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R15" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,7 +2479,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2475,7 +2489,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,27 +2508,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,62 +2526,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R16" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2596,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2621,12 +2606,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2620,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3286,38 +3286,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R22" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,7 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3386,6 +3391,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3403,10 +3428,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3414,27 +3439,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3443,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R23" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,12 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3512,22 +3537,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,27 +3570,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>58019</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3573,10 +3598,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3585,13 +3624,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R24" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3620,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3630,12 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3649,27 +3683,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3687,10 +3701,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>58019</v>
+        <v>98345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3698,41 +3712,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R25" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125811550</v>
+        <v>125813307</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>80105</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,36 +1199,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1237,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478765</v>
+        <v>478954</v>
       </c>
       <c r="R6" t="n">
-        <v>7027416</v>
+        <v>7027278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1282,12 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1287,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,50 +1325,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813534</v>
+        <v>125812909</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>80070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478904</v>
+        <v>478839</v>
       </c>
       <c r="R7" t="n">
-        <v>7027279</v>
+        <v>7027172</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1394,7 +1395,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1405,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,6 +1425,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1436,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125814202</v>
+        <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>98354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,27 +1473,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,13 +1511,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478726</v>
+        <v>478765</v>
       </c>
       <c r="R8" t="n">
-        <v>7027177</v>
+        <v>7027416</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1511,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1521,7 +1556,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1535,7 +1575,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1553,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125813307</v>
+        <v>125813534</v>
       </c>
       <c r="B9" t="n">
-        <v>80105</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,27 +1604,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1593,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478954</v>
+        <v>478904</v>
       </c>
       <c r="R9" t="n">
-        <v>7027278</v>
+        <v>7027279</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1628,7 +1668,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,7 +1678,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,26 +1693,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1690,45 +1710,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125812909</v>
+        <v>125814202</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478839</v>
+        <v>478726</v>
       </c>
       <c r="R10" t="n">
-        <v>7027172</v>
+        <v>7027177</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1760,7 +1785,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1770,12 +1795,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,26 +1810,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125814842</v>
+        <v>125813429</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -2008,19 +2008,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478567</v>
+        <v>478954</v>
       </c>
       <c r="R12" t="n">
-        <v>7027140</v>
+        <v>7027265</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2059,12 +2064,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2116,7 +2121,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125813429</v>
+        <v>125814842</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -2150,24 +2155,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478954</v>
+        <v>478567</v>
       </c>
       <c r="R13" t="n">
-        <v>7027265</v>
+        <v>7027140</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2395,62 +2395,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>98347</v>
+        <v>78967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R15" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2479,7 +2465,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2489,12 +2475,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,7 +2489,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2526,48 +2527,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>98354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R16" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2596,7 +2611,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2606,7 +2621,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2620,27 +2640,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,62 +2658,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>98241</v>
+        <v>80070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R17" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2742,7 +2728,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2752,12 +2738,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,7 +2757,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2789,48 +2795,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>98248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R18" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2879,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,12 +2889,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,27 +2908,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3428,27 +3428,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B23" t="n">
-        <v>57648</v>
+        <v>58019</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3456,10 +3456,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3482,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R23" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3517,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3527,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3532,27 +3541,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3570,27 +3559,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125811849</v>
+        <v>125813824</v>
       </c>
       <c r="B24" t="n">
-        <v>58019</v>
+        <v>57648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3598,24 +3587,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3624,13 +3599,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478799</v>
+        <v>478869</v>
       </c>
       <c r="R24" t="n">
-        <v>7027381</v>
+        <v>7027250</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3659,7 +3634,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3644,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3683,7 +3663,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3704,7 +3704,7 @@
         <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98347</v>
+        <v>98354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98230</v>
+        <v>98237</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -2395,48 +2395,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>98354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R15" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,7 +2479,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2475,7 +2489,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,27 +2508,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,62 +2526,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B16" t="n">
-        <v>98354</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R16" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2596,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2621,12 +2606,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2620,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,48 +2658,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B17" t="n">
-        <v>80070</v>
+        <v>98248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R17" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2728,7 +2742,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2738,12 +2752,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,27 +2771,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2795,62 +2789,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B18" t="n">
-        <v>98248</v>
+        <v>80070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R18" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2879,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2889,12 +2869,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2908,7 +2888,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R22" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,52 +3428,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125811849</v>
+        <v>125812974</v>
       </c>
       <c r="B23" t="n">
-        <v>58019</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3482,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478799</v>
+        <v>478846</v>
       </c>
       <c r="R23" t="n">
-        <v>7027381</v>
+        <v>7027184</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3517,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3527,7 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3541,7 +3532,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3559,27 +3570,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>58019</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3587,10 +3598,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3599,13 +3624,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R24" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3634,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3644,12 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3663,27 +3683,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125812928</v>
       </c>
       <c r="B4" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>125813307</v>
       </c>
       <c r="B6" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>125812909</v>
       </c>
       <c r="B7" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R9" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125814202</v>
+        <v>125813534</v>
       </c>
       <c r="B10" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478726</v>
+        <v>478904</v>
       </c>
       <c r="R10" t="n">
-        <v>7027177</v>
+        <v>7027279</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2266,7 +2266,7 @@
         <v>125810800</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2395,62 +2395,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>98354</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R15" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2479,7 +2465,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2489,12 +2475,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,7 +2489,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2526,48 +2527,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>98355</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R16" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2596,7 +2611,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2606,7 +2621,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2620,27 +2640,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,62 +2658,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>98248</v>
+        <v>80071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R17" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2742,7 +2728,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2752,12 +2738,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,7 +2757,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2789,48 +2795,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>98249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R18" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2879,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,12 +2889,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,27 +2908,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125813824</v>
+        <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>57648</v>
+        <v>80071</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478869</v>
+        <v>478846</v>
       </c>
       <c r="R22" t="n">
-        <v>7027250</v>
+        <v>7027184</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>57648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,27 +3439,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R23" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3537,22 +3537,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3573,7 +3573,7 @@
         <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125814707</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>125813374</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>125813877</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98664</v>
+        <v>98665</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98354</v>
+        <v>98355</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98237</v>
+        <v>98238</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125811550</v>
+        <v>125813534</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1473,36 +1473,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1511,13 +1502,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478765</v>
+        <v>478904</v>
       </c>
       <c r="R8" t="n">
-        <v>7027416</v>
+        <v>7027279</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,7 +1537,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,12 +1547,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,7 +1561,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,7 +1582,7 @@
         <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1710,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125813534</v>
+        <v>125811550</v>
       </c>
       <c r="B10" t="n">
-        <v>98353</v>
+        <v>98357</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,27 +1707,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1750,13 +1745,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478904</v>
+        <v>478765</v>
       </c>
       <c r="R10" t="n">
-        <v>7027279</v>
+        <v>7027416</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1795,7 +1790,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125813429</v>
+        <v>125814842</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -2008,24 +2008,19 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478954</v>
+        <v>478567</v>
       </c>
       <c r="R12" t="n">
-        <v>7027265</v>
+        <v>7027140</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2054,7 +2049,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2064,12 +2059,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,7 +2116,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125814842</v>
+        <v>125813429</v>
       </c>
       <c r="B13" t="n">
         <v>57651</v>
@@ -2155,19 +2150,24 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478567</v>
+        <v>478954</v>
       </c>
       <c r="R13" t="n">
-        <v>7027140</v>
+        <v>7027265</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,38 +3286,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125812974</v>
+        <v>125814512</v>
       </c>
       <c r="B22" t="n">
-        <v>80071</v>
+        <v>98355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478846</v>
+        <v>478607</v>
       </c>
       <c r="R22" t="n">
-        <v>7027184</v>
+        <v>7027167</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3391,26 +3386,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,27 +3403,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B23" t="n">
-        <v>57648</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3456,10 +3431,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3457,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R23" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3492,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3502,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3532,27 +3516,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3570,27 +3534,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125811849</v>
+        <v>125813824</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>57648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3598,24 +3562,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3624,13 +3574,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478799</v>
+        <v>478869</v>
       </c>
       <c r="R24" t="n">
-        <v>7027381</v>
+        <v>7027250</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3659,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3619,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3683,7 +3638,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3701,38 +3676,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B25" t="n">
-        <v>98353</v>
+        <v>80071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,13 +3716,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R25" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3776,7 +3751,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3761,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3801,6 +3781,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98665</v>
+        <v>98667</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98238</v>
+        <v>98240</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -2395,48 +2395,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>98357</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R15" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,7 +2479,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2475,7 +2489,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,27 +2508,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,62 +2526,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R16" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2596,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2621,12 +2606,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2620,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125812928</v>
       </c>
       <c r="B4" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>125813307</v>
       </c>
       <c r="B6" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>125812909</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>125813534</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>125811550</v>
       </c>
       <c r="B10" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125810800</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2395,62 +2395,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>98357</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R15" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2479,7 +2465,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2489,12 +2475,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,7 +2489,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2526,48 +2527,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R16" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2596,7 +2611,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2606,7 +2621,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2620,27 +2640,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,48 +2658,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B17" t="n">
-        <v>80071</v>
+        <v>98255</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R17" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2728,7 +2742,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2738,12 +2752,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,27 +2771,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2795,62 +2789,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B18" t="n">
-        <v>98251</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R18" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2879,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2889,12 +2869,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2908,7 +2888,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,38 +3286,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125814512</v>
+        <v>125813824</v>
       </c>
       <c r="B22" t="n">
-        <v>98355</v>
+        <v>57648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478607</v>
+        <v>478869</v>
       </c>
       <c r="R22" t="n">
-        <v>7027167</v>
+        <v>7027250</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,7 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3386,6 +3391,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3403,52 +3428,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125811849</v>
+        <v>125812974</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3457,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478799</v>
+        <v>478846</v>
       </c>
       <c r="R23" t="n">
-        <v>7027381</v>
+        <v>7027184</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3492,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3502,7 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3516,7 +3532,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3534,38 +3570,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125813824</v>
+        <v>125814512</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>98359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3574,13 +3610,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478869</v>
+        <v>478607</v>
       </c>
       <c r="R24" t="n">
-        <v>7027250</v>
+        <v>7027167</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3645,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,12 +3655,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3639,26 +3670,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,38 +3687,52 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125812974</v>
+        <v>125811849</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>58020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3716,13 +3741,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478846</v>
+        <v>478799</v>
       </c>
       <c r="R25" t="n">
-        <v>7027184</v>
+        <v>7027381</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3751,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3761,12 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3780,27 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125814707</v>
+        <v>125813374</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3946,37 +3946,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478571</v>
+        <v>478958</v>
       </c>
       <c r="R27" t="n">
-        <v>7027142</v>
+        <v>7027272</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4005,7 +4010,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4015,7 +4020,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4034,22 +4039,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4067,10 +4072,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125813374</v>
+        <v>125814707</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4078,42 +4083,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478958</v>
+        <v>478571</v>
       </c>
       <c r="R28" t="n">
-        <v>7027272</v>
+        <v>7027142</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         <v>125813877</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98667</v>
+        <v>98671</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98240</v>
+        <v>98244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1188,53 +1188,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125813307</v>
+        <v>125812909</v>
       </c>
       <c r="B6" t="n">
-        <v>80110</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478954</v>
+        <v>478839</v>
       </c>
       <c r="R6" t="n">
-        <v>7027278</v>
+        <v>7027172</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,48 +1325,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125812909</v>
+        <v>125813307</v>
       </c>
       <c r="B7" t="n">
-        <v>80075</v>
+        <v>80110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478839</v>
+        <v>478954</v>
       </c>
       <c r="R7" t="n">
-        <v>7027172</v>
+        <v>7027278</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1395,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1405,12 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125813534</v>
+        <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98359</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,27 +1473,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1502,13 +1511,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478904</v>
+        <v>478765</v>
       </c>
       <c r="R8" t="n">
-        <v>7027279</v>
+        <v>7027416</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1537,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1547,7 +1556,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,7 +1575,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1582,7 +1596,7 @@
         <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1696,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125811550</v>
+        <v>125813534</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>98360</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,36 +1721,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1745,13 +1750,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478765</v>
+        <v>478904</v>
       </c>
       <c r="R10" t="n">
-        <v>7027416</v>
+        <v>7027279</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1790,12 +1795,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>125814170</v>
       </c>
       <c r="B17" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125813824</v>
+        <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>57648</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478869</v>
+        <v>478846</v>
       </c>
       <c r="R22" t="n">
-        <v>7027250</v>
+        <v>7027184</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>57648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,27 +3439,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R23" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3537,22 +3537,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125814512</v>
+        <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>98359</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3581,27 +3581,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3610,10 +3624,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478607</v>
+        <v>478799</v>
       </c>
       <c r="R24" t="n">
-        <v>7027167</v>
+        <v>7027381</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3645,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3655,7 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3669,7 +3683,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3687,10 +3701,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>58020</v>
+        <v>98360</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3698,41 +3712,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R25" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125813374</v>
+        <v>125814707</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3946,42 +3946,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478958</v>
+        <v>478571</v>
       </c>
       <c r="R27" t="n">
-        <v>7027272</v>
+        <v>7027142</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4010,7 +4005,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4020,7 +4015,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4039,22 +4034,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4072,10 +4067,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125814707</v>
+        <v>125813374</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4083,37 +4078,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478571</v>
+        <v>478958</v>
       </c>
       <c r="R28" t="n">
-        <v>7027142</v>
+        <v>7027272</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98671</v>
+        <v>98672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98361</v>
+        <v>98362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98244</v>
+        <v>98245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -2395,48 +2395,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R15" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2465,7 +2479,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2475,7 +2489,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,27 +2508,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,62 +2526,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B16" t="n">
-        <v>98362</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R16" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2596,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2621,12 +2606,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2620,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125812928</v>
       </c>
       <c r="B4" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,48 +1188,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125812909</v>
+        <v>125813307</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478839</v>
+        <v>478954</v>
       </c>
       <c r="R6" t="n">
-        <v>7027172</v>
+        <v>7027278</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,53 +1325,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813307</v>
+        <v>125812909</v>
       </c>
       <c r="B7" t="n">
-        <v>80110</v>
+        <v>80076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478954</v>
+        <v>478839</v>
       </c>
       <c r="R7" t="n">
-        <v>7027278</v>
+        <v>7027172</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1395,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1405,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
         <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125814202</v>
+        <v>125813534</v>
       </c>
       <c r="B9" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478726</v>
+        <v>478904</v>
       </c>
       <c r="R9" t="n">
-        <v>7027177</v>
+        <v>7027279</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B10" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R10" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1830,7 +1830,7 @@
         <v>125812647</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>125814842</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>125813429</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125810800</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2395,62 +2395,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125814085</v>
+        <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478739</v>
+        <v>478904</v>
       </c>
       <c r="R15" t="n">
-        <v>7027152</v>
+        <v>7027272</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2479,7 +2465,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2489,12 +2475,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>21:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2508,7 +2489,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2526,48 +2527,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125813564</v>
+        <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>98364</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478904</v>
+        <v>478739</v>
       </c>
       <c r="R16" t="n">
-        <v>7027272</v>
+        <v>7027152</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2596,7 +2611,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2606,7 +2621,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2620,27 +2640,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2661,7 +2661,7 @@
         <v>125814170</v>
       </c>
       <c r="B17" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>125813002</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
         <v>125813824</v>
       </c>
       <c r="B23" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125814707</v>
+        <v>125813374</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3946,37 +3946,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478571</v>
+        <v>478958</v>
       </c>
       <c r="R27" t="n">
-        <v>7027142</v>
+        <v>7027272</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4005,7 +4010,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4015,7 +4020,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4034,22 +4039,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4067,10 +4072,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125813374</v>
+        <v>125814707</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4078,42 +4083,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478958</v>
+        <v>478571</v>
       </c>
       <c r="R28" t="n">
-        <v>7027272</v>
+        <v>7027142</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         <v>125813877</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98672</v>
+        <v>98674</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>125812517</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -2658,62 +2658,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>98258</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R17" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2742,7 +2728,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2752,12 +2738,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,7 +2757,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2789,48 +2795,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>98258</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R18" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2879,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,12 +2889,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,27 +2908,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3935,10 +3935,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125813374</v>
+        <v>125814707</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3946,42 +3946,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478958</v>
+        <v>478571</v>
       </c>
       <c r="R27" t="n">
-        <v>7027272</v>
+        <v>7027142</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4010,7 +4005,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4020,7 +4015,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4039,22 +4034,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4072,10 +4067,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125814707</v>
+        <v>125813374</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4083,37 +4078,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478571</v>
+        <v>478958</v>
       </c>
       <c r="R28" t="n">
-        <v>7027142</v>
+        <v>7027272</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4171,22 +4171,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1188,53 +1188,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125813307</v>
+        <v>125812909</v>
       </c>
       <c r="B6" t="n">
-        <v>80111</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478954</v>
+        <v>478839</v>
       </c>
       <c r="R6" t="n">
-        <v>7027278</v>
+        <v>7027172</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,7 +1258,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1268,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,48 +1325,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125812909</v>
+        <v>125813307</v>
       </c>
       <c r="B7" t="n">
-        <v>80076</v>
+        <v>80111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478839</v>
+        <v>478954</v>
       </c>
       <c r="R7" t="n">
-        <v>7027172</v>
+        <v>7027278</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1395,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1405,12 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
         <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>125813534</v>
       </c>
       <c r="B9" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>125814202</v>
       </c>
       <c r="B10" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98674</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -1462,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125811550</v>
+        <v>125813534</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,36 +1473,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1511,13 +1502,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478765</v>
+        <v>478904</v>
       </c>
       <c r="R8" t="n">
-        <v>7027416</v>
+        <v>7027279</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,7 +1537,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,12 +1547,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,7 +1561,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B9" t="n">
         <v>98364</v>
@@ -1624,7 +1610,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1633,10 +1619,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R9" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1668,7 +1654,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1678,7 +1664,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,10 +1696,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125814202</v>
+        <v>125811550</v>
       </c>
       <c r="B10" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,27 +1707,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1750,13 +1745,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478726</v>
+        <v>478765</v>
       </c>
       <c r="R10" t="n">
-        <v>7027177</v>
+        <v>7027416</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1785,7 +1780,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1795,7 +1790,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>125813534</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>125811550</v>
       </c>
       <c r="B10" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -1325,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813307</v>
+        <v>125813534</v>
       </c>
       <c r="B7" t="n">
-        <v>80111</v>
+        <v>98366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,27 +1336,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478954</v>
+        <v>478904</v>
       </c>
       <c r="R7" t="n">
-        <v>7027278</v>
+        <v>7027279</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,26 +1425,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,7 +1442,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B8" t="n">
         <v>98366</v>
@@ -1493,7 +1473,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1502,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R8" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1537,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1547,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125814202</v>
+        <v>125811550</v>
       </c>
       <c r="B9" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,27 +1570,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1619,13 +1608,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478726</v>
+        <v>478765</v>
       </c>
       <c r="R9" t="n">
-        <v>7027177</v>
+        <v>7027416</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1654,7 +1643,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1664,7 +1653,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1678,7 +1672,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1696,10 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125811550</v>
+        <v>125813307</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>80111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1707,36 +1701,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219847</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1745,10 +1730,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478765</v>
+        <v>478954</v>
       </c>
       <c r="R10" t="n">
-        <v>7027416</v>
+        <v>7027278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1780,7 +1765,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1790,12 +1775,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1809,7 +1789,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125812928</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>125812909</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813534</v>
+        <v>125813307</v>
       </c>
       <c r="B7" t="n">
-        <v>98366</v>
+        <v>80115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,27 +1336,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478904</v>
+        <v>478954</v>
       </c>
       <c r="R7" t="n">
-        <v>7027279</v>
+        <v>7027278</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,6 +1425,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,10 +1462,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125814202</v>
+        <v>125811550</v>
       </c>
       <c r="B8" t="n">
-        <v>98366</v>
+        <v>98372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,27 +1473,36 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1482,13 +1511,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478726</v>
+        <v>478765</v>
       </c>
       <c r="R8" t="n">
-        <v>7027177</v>
+        <v>7027416</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1556,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,7 +1575,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1559,10 +1593,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125811550</v>
+        <v>125814202</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,36 +1604,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1608,13 +1633,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478765</v>
+        <v>478726</v>
       </c>
       <c r="R9" t="n">
-        <v>7027416</v>
+        <v>7027177</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1643,7 +1668,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1653,12 +1678,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1672,7 +1692,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1690,10 +1710,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125813307</v>
+        <v>125813534</v>
       </c>
       <c r="B10" t="n">
-        <v>80111</v>
+        <v>98370</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,27 +1721,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1730,13 +1750,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478954</v>
+        <v>478904</v>
       </c>
       <c r="R10" t="n">
-        <v>7027278</v>
+        <v>7027279</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1765,7 +1785,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1775,7 +1795,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1790,26 +1810,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
         <v>125812647</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>125814842</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>125813429</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125810800</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,38 +3286,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125812974</v>
+        <v>125814512</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>98370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478846</v>
+        <v>478607</v>
       </c>
       <c r="R22" t="n">
-        <v>7027184</v>
+        <v>7027167</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3391,26 +3386,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,10 +3403,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125813824</v>
+        <v>125812974</v>
       </c>
       <c r="B23" t="n">
-        <v>57649</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,27 +3414,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3443,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478869</v>
+        <v>478846</v>
       </c>
       <c r="R23" t="n">
-        <v>7027250</v>
+        <v>7027184</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3488,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3537,22 +3512,22 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3570,27 +3545,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125811849</v>
+        <v>125813824</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>57653</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3598,24 +3573,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3624,13 +3585,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478799</v>
+        <v>478869</v>
       </c>
       <c r="R24" t="n">
-        <v>7027381</v>
+        <v>7027250</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3659,7 +3620,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3630,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3683,7 +3649,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3701,10 +3687,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125814512</v>
+        <v>125811849</v>
       </c>
       <c r="B25" t="n">
-        <v>98366</v>
+        <v>58025</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3712,27 +3698,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478607</v>
+        <v>478799</v>
       </c>
       <c r="R25" t="n">
-        <v>7027167</v>
+        <v>7027381</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125814707</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>125813374</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>125813877</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>125812517</v>
       </c>
       <c r="B32" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -1188,48 +1188,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125812909</v>
+        <v>125811550</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>98372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478839</v>
+        <v>478765</v>
       </c>
       <c r="R6" t="n">
-        <v>7027172</v>
+        <v>7027416</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1258,7 +1272,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1268,12 +1282,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,27 +1301,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813307</v>
+        <v>125814202</v>
       </c>
       <c r="B7" t="n">
-        <v>80115</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,27 +1330,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1365,13 +1359,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478954</v>
+        <v>478726</v>
       </c>
       <c r="R7" t="n">
-        <v>7027278</v>
+        <v>7027177</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,26 +1419,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,62 +1436,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125811550</v>
+        <v>125812909</v>
       </c>
       <c r="B8" t="n">
-        <v>98372</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478765</v>
+        <v>478839</v>
       </c>
       <c r="R8" t="n">
-        <v>7027416</v>
+        <v>7027172</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1546,7 +1506,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,12 +1516,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Minst 4 plantor.</t>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1575,7 +1535,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1593,10 +1573,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125814202</v>
+        <v>125813307</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>80115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1604,27 +1584,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1633,13 +1613,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478726</v>
+        <v>478954</v>
       </c>
       <c r="R9" t="n">
-        <v>7027177</v>
+        <v>7027278</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1668,7 +1648,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1678,7 +1658,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1693,6 +1673,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -3286,38 +3286,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R22" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,7 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3386,6 +3391,26 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3403,38 +3428,52 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125812974</v>
+        <v>125811849</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>58025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3443,13 +3482,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478846</v>
+        <v>478799</v>
       </c>
       <c r="R23" t="n">
-        <v>7027184</v>
+        <v>7027381</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3478,7 +3517,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3488,12 +3527,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3507,27 +3541,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,38 +3559,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125813824</v>
+        <v>125814512</v>
       </c>
       <c r="B24" t="n">
-        <v>57653</v>
+        <v>98370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3585,13 +3599,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478869</v>
+        <v>478607</v>
       </c>
       <c r="R24" t="n">
-        <v>7027250</v>
+        <v>7027167</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3620,7 +3634,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3630,12 +3644,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3650,26 +3659,6 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3687,27 +3676,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125811849</v>
+        <v>125813824</v>
       </c>
       <c r="B25" t="n">
-        <v>58025</v>
+        <v>57653</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3715,24 +3704,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,13 +3716,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478799</v>
+        <v>478869</v>
       </c>
       <c r="R25" t="n">
-        <v>7027381</v>
+        <v>7027250</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3776,7 +3751,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3761,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,7 +3780,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>125811550</v>
       </c>
       <c r="B6" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125814202</v>
+        <v>125813534</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478726</v>
+        <v>478904</v>
       </c>
       <c r="R7" t="n">
-        <v>7027177</v>
+        <v>7027279</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,45 +1436,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125812909</v>
+        <v>125814202</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>98373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478839</v>
+        <v>478726</v>
       </c>
       <c r="R8" t="n">
-        <v>7027172</v>
+        <v>7027177</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1506,7 +1511,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1516,12 +1521,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1536,26 +1536,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Bark på dött träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1710,50 +1690,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125813534</v>
+        <v>125812909</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478904</v>
+        <v>478839</v>
       </c>
       <c r="R10" t="n">
-        <v>7027279</v>
+        <v>7027172</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1785,7 +1760,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1795,7 +1770,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1810,6 +1790,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2658,48 +2658,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>98269</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R17" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2728,7 +2742,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2738,12 +2752,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,27 +2771,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2795,62 +2789,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B18" t="n">
-        <v>98266</v>
+        <v>80080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R18" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2879,7 +2859,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2889,12 +2869,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2908,7 +2888,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>57653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R22" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B23" t="n">
-        <v>58025</v>
+        <v>98373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,41 +3439,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3482,10 +3468,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R23" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3517,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3527,7 +3513,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3541,7 +3527,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3559,38 +3545,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B24" t="n">
-        <v>98370</v>
+        <v>80080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3599,13 +3585,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R24" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3634,7 +3620,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3644,7 +3630,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3659,6 +3650,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,27 +3687,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B25" t="n">
-        <v>57653</v>
+        <v>58025</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3704,10 +3715,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3716,13 +3741,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R25" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3751,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3761,12 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3780,27 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98682</v>
+        <v>98685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98372</v>
+        <v>98375</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98255</v>
+        <v>98258</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125813824</v>
+        <v>125812974</v>
       </c>
       <c r="B22" t="n">
-        <v>57653</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478869</v>
+        <v>478846</v>
       </c>
       <c r="R22" t="n">
-        <v>7027250</v>
+        <v>7027184</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,38 +3428,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125814512</v>
+        <v>125813824</v>
       </c>
       <c r="B23" t="n">
-        <v>98373</v>
+        <v>57653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478607</v>
+        <v>478869</v>
       </c>
       <c r="R23" t="n">
-        <v>7027167</v>
+        <v>7027250</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,7 +3513,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3528,6 +3533,26 @@
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3545,38 +3570,52 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125812974</v>
+        <v>125811849</v>
       </c>
       <c r="B24" t="n">
-        <v>80080</v>
+        <v>58025</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3585,13 +3624,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478846</v>
+        <v>478799</v>
       </c>
       <c r="R24" t="n">
-        <v>7027184</v>
+        <v>7027381</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3620,7 +3659,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3630,12 +3669,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:32</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3649,27 +3683,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3687,10 +3701,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B25" t="n">
-        <v>58025</v>
+        <v>98373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3698,41 +3712,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R25" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -1319,7 +1319,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B7" t="n">
         <v>98373</v>
@@ -1350,7 +1350,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R7" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,7 +1436,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125814202</v>
+        <v>125813534</v>
       </c>
       <c r="B8" t="n">
         <v>98373</v>
@@ -1467,7 +1467,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478726</v>
+        <v>478904</v>
       </c>
       <c r="R8" t="n">
-        <v>7027177</v>
+        <v>7027279</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2658,62 +2658,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125814170</v>
+        <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>80080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478760</v>
+        <v>478841</v>
       </c>
       <c r="R17" t="n">
-        <v>7027150</v>
+        <v>7027177</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2742,7 +2728,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2752,12 +2738,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,7 +2757,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2789,48 +2795,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125813002</v>
+        <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>80080</v>
+        <v>98269</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478841</v>
+        <v>478760</v>
       </c>
       <c r="R18" t="n">
-        <v>7027177</v>
+        <v>7027150</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2859,7 +2879,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2869,12 +2889,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2888,27 +2908,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>57653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3297,27 +3297,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R22" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3395,22 +3395,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,27 +3428,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B23" t="n">
-        <v>57653</v>
+        <v>58025</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3456,10 +3456,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3468,13 +3482,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R23" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3503,7 +3517,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3513,12 +3527,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3532,27 +3541,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3570,10 +3559,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B24" t="n">
-        <v>58025</v>
+        <v>98373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3581,41 +3570,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3624,10 +3599,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R24" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3659,7 +3634,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3669,7 +3644,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3683,7 +3658,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3701,38 +3676,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B25" t="n">
-        <v>98373</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3741,13 +3716,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R25" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3776,7 +3751,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3786,7 +3761,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3801,6 +3781,26 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125811939</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>125811591</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>125812928</v>
       </c>
       <c r="B4" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125811550</v>
+        <v>125813307</v>
       </c>
       <c r="B6" t="n">
-        <v>98375</v>
+        <v>80118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1199,36 +1199,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1237,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478765</v>
+        <v>478954</v>
       </c>
       <c r="R6" t="n">
-        <v>7027416</v>
+        <v>7027278</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1272,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1282,12 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 4 plantor.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1301,7 +1287,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1319,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125814202</v>
+        <v>125813534</v>
       </c>
       <c r="B7" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1356,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1359,10 +1365,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478726</v>
+        <v>478904</v>
       </c>
       <c r="R7" t="n">
-        <v>7027177</v>
+        <v>7027279</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1394,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1404,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1436,10 +1442,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125813534</v>
+        <v>125814202</v>
       </c>
       <c r="B8" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1473,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1476,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478904</v>
+        <v>478726</v>
       </c>
       <c r="R8" t="n">
-        <v>7027279</v>
+        <v>7027177</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1511,7 +1517,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1521,7 +1527,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125813307</v>
+        <v>125811550</v>
       </c>
       <c r="B9" t="n">
-        <v>80115</v>
+        <v>98384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,27 +1570,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1593,10 +1608,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478954</v>
+        <v>478765</v>
       </c>
       <c r="R9" t="n">
-        <v>7027278</v>
+        <v>7027416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1643,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1638,7 +1653,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,27 +1672,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1693,7 +1693,7 @@
         <v>125812909</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>125812647</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>125814842</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>125813429</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>125810800</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>125813564</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>125814085</v>
       </c>
       <c r="B16" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>125813002</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>125814170</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>125811877</v>
       </c>
       <c r="B19" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>125812706</v>
       </c>
       <c r="B20" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>125814305</v>
       </c>
       <c r="B21" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3286,27 +3286,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125813824</v>
+        <v>125811849</v>
       </c>
       <c r="B22" t="n">
-        <v>57653</v>
+        <v>58027</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3314,10 +3314,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3326,13 +3340,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478869</v>
+        <v>478799</v>
       </c>
       <c r="R22" t="n">
-        <v>7027250</v>
+        <v>7027381</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3361,7 +3375,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3371,12 +3385,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3390,27 +3399,7 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3428,10 +3417,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125811849</v>
+        <v>125814512</v>
       </c>
       <c r="B23" t="n">
-        <v>58025</v>
+        <v>98382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3439,41 +3428,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3482,10 +3457,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478799</v>
+        <v>478607</v>
       </c>
       <c r="R23" t="n">
-        <v>7027381</v>
+        <v>7027167</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3517,7 +3492,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3527,7 +3502,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3541,7 +3516,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3559,38 +3534,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125814512</v>
+        <v>125812974</v>
       </c>
       <c r="B24" t="n">
-        <v>98373</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3599,13 +3574,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478607</v>
+        <v>478846</v>
       </c>
       <c r="R24" t="n">
-        <v>7027167</v>
+        <v>7027184</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3634,7 +3609,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3644,7 +3619,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3659,6 +3639,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,10 +3676,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125812974</v>
+        <v>125813824</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3687,27 +3687,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3716,13 +3716,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478846</v>
+        <v>478869</v>
       </c>
       <c r="R25" t="n">
-        <v>7027184</v>
+        <v>7027250</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3785,22 +3785,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3821,7 +3821,7 @@
         <v>125813227</v>
       </c>
       <c r="B26" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>125814707</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>125813374</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>125813877</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>125832601</v>
       </c>
       <c r="B30" t="n">
-        <v>98685</v>
+        <v>98694</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         <v>125832607</v>
       </c>
       <c r="B31" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>125812517</v>
       </c>
       <c r="B32" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>125832700</v>
       </c>
       <c r="B33" t="n">
-        <v>98375</v>
+        <v>98384</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>125815143</v>
       </c>
       <c r="B34" t="n">
-        <v>98258</v>
+        <v>98267</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125811939</v>
+        <v>125815143</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478813</v>
+        <v>478555</v>
       </c>
       <c r="R2" t="n">
-        <v>7027365</v>
+        <v>7027087</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst 36 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +788,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125811591</v>
+        <v>125815433</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,27 +817,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>504</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478763</v>
+        <v>478625</v>
       </c>
       <c r="R3" t="n">
-        <v>7027381</v>
+        <v>7027030</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +905,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>21:49</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 9 plantor inom ca 0,5m2 yta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +942,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125812928</v>
+        <v>125810800</v>
       </c>
       <c r="B4" t="n">
-        <v>80119</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Albanobodarna, Albanobodarna, Jmt</t>
+          <t>Kvarnmyren, Kvarnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478841</v>
+        <v>478950</v>
       </c>
       <c r="R4" t="n">
-        <v>7027170</v>
+        <v>7027384</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +1012,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1022,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,27 +1036,27 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1054,11 +1077,11 @@
         <v>125811759</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1188,27 +1211,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125813307</v>
+        <v>125813564</v>
       </c>
       <c r="B6" t="n">
-        <v>80118</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1217,24 +1240,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478954</v>
+        <v>478904</v>
       </c>
       <c r="R6" t="n">
-        <v>7027278</v>
+        <v>7027272</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,7 +1281,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1291,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,22 +1310,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,53 +1343,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125813534</v>
+        <v>125813877</v>
       </c>
       <c r="B7" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478904</v>
+        <v>478823</v>
       </c>
       <c r="R7" t="n">
-        <v>7027279</v>
+        <v>7027253</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1400,7 +1413,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1410,7 +1423,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,6 +1438,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,53 +1475,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125814202</v>
+        <v>125814707</v>
       </c>
       <c r="B8" t="n">
-        <v>98382</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478726</v>
+        <v>478571</v>
       </c>
       <c r="R8" t="n">
-        <v>7027177</v>
+        <v>7027142</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1517,7 +1545,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1527,7 +1555,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,6 +1570,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1559,62 +1607,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125811550</v>
+        <v>125812909</v>
       </c>
       <c r="B9" t="n">
-        <v>98384</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478765</v>
+        <v>478839</v>
       </c>
       <c r="R9" t="n">
-        <v>7027416</v>
+        <v>7027172</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1643,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1653,12 +1687,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 4 plantor.</t>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1672,7 +1706,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1690,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125812909</v>
+        <v>125812974</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,16 +1773,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478839</v>
+        <v>478846</v>
       </c>
       <c r="R10" t="n">
-        <v>7027172</v>
+        <v>7027184</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1760,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1770,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en grov sälglåga.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1804,12 +1863,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1827,10 +1886,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125812647</v>
+        <v>125813002</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,47 +1897,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478776</v>
+        <v>478841</v>
       </c>
       <c r="R11" t="n">
-        <v>7027210</v>
+        <v>7027177</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1907,7 +1956,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1917,12 +1966,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1951,12 +2000,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1974,10 +2023,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125814842</v>
+        <v>125813374</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1985,27 +2034,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2014,13 +2063,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478567</v>
+        <v>478958</v>
       </c>
       <c r="R12" t="n">
-        <v>7027140</v>
+        <v>7027272</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2049,7 +2098,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2059,12 +2108,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>21:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2083,22 +2127,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2116,43 +2160,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125813429</v>
+        <v>125813307</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2164,10 +2203,10 @@
         <v>478954</v>
       </c>
       <c r="R13" t="n">
-        <v>7027265</v>
+        <v>7027278</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2196,7 +2235,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2206,12 +2245,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen.</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,22 +2264,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2263,48 +2297,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125810800</v>
+        <v>125812928</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>80468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Kvarnmyren, Jmt</t>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478950</v>
+        <v>478841</v>
       </c>
       <c r="R14" t="n">
-        <v>7027384</v>
+        <v>7027170</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2333,7 +2372,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2343,7 +2382,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på en grov sälglåga.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2357,27 +2401,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2395,45 +2439,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125813564</v>
+        <v>125813824</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478904</v>
+        <v>478869</v>
       </c>
       <c r="R15" t="n">
-        <v>7027272</v>
+        <v>7027250</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2465,7 +2514,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2475,7 +2524,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rejäla hackspår i död gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2504,12 +2558,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2527,47 +2581,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125814085</v>
+        <v>125812517</v>
       </c>
       <c r="B16" t="n">
-        <v>98384</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2576,13 +2626,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478739</v>
+        <v>478769</v>
       </c>
       <c r="R16" t="n">
-        <v>7027152</v>
+        <v>7027240</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2611,7 +2661,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2621,12 +2671,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen av en död gran som delvis är avbarkad troligen p.g.a födosökande tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,7 +2690,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2658,10 +2728,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125813002</v>
+        <v>125812647</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2669,37 +2739,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478841</v>
+        <v>478776</v>
       </c>
       <c r="R17" t="n">
-        <v>7027177</v>
+        <v>7027210</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2728,7 +2808,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2738,12 +2818,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,12 +2852,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2795,47 +2875,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125814170</v>
+        <v>125813429</v>
       </c>
       <c r="B18" t="n">
-        <v>98278</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2844,13 +2920,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478760</v>
+        <v>478954</v>
       </c>
       <c r="R18" t="n">
-        <v>7027150</v>
+        <v>7027265</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2879,7 +2955,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2889,12 +2965,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>21:12</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
+          <t>Ringhack, äldre, på stambasen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2908,7 +2984,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2926,38 +3022,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125811877</v>
+        <v>125814666</v>
       </c>
       <c r="B19" t="n">
-        <v>98384</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2966,13 +3062,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478820</v>
+        <v>478567</v>
       </c>
       <c r="R19" t="n">
-        <v>7027379</v>
+        <v>7027155</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3001,7 +3097,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3011,7 +3107,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>21:24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3025,7 +3126,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3043,38 +3164,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125812706</v>
+        <v>125814842</v>
       </c>
       <c r="B20" t="n">
-        <v>98382</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3083,10 +3204,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478787</v>
+        <v>478567</v>
       </c>
       <c r="R20" t="n">
-        <v>7027200</v>
+        <v>7027140</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3118,7 +3239,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3128,7 +3249,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>21:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3143,6 +3269,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3160,10 +3306,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125814305</v>
+        <v>132795678</v>
       </c>
       <c r="B21" t="n">
-        <v>98384</v>
+        <v>57162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3171,36 +3317,41 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3209,13 +3360,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478668</v>
+        <v>478908</v>
       </c>
       <c r="R21" t="n">
-        <v>7027201</v>
+        <v>7027152</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3239,22 +3390,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3265,21 +3416,16 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annelie Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Annelie Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3289,7 +3435,7 @@
         <v>125811849</v>
       </c>
       <c r="B22" t="n">
-        <v>58027</v>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3417,10 +3563,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125814512</v>
+        <v>125814170</v>
       </c>
       <c r="B23" t="n">
-        <v>98382</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3428,27 +3574,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3457,13 +3612,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478607</v>
+        <v>478760</v>
       </c>
       <c r="R23" t="n">
-        <v>7027167</v>
+        <v>7027150</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3492,7 +3647,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3502,7 +3657,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor inom 3 x 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3516,7 +3676,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3534,38 +3694,47 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125812974</v>
+        <v>125811550</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>99142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3574,13 +3743,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478846</v>
+        <v>478765</v>
       </c>
       <c r="R24" t="n">
-        <v>7027184</v>
+        <v>7027416</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3609,7 +3778,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3619,12 +3788,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Minst 4 plantor.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3638,27 +3807,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3676,38 +3825,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125813824</v>
+        <v>125811877</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>99142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>219847</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3716,13 +3865,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478869</v>
+        <v>478820</v>
       </c>
       <c r="R25" t="n">
-        <v>7027250</v>
+        <v>7027379</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3751,7 +3900,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3761,12 +3910,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:59</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rejäla hackspår i död gran.</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3780,27 +3924,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3818,10 +3942,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125813227</v>
+        <v>125814085</v>
       </c>
       <c r="B26" t="n">
-        <v>98382</v>
+        <v>99142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3829,27 +3953,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3858,13 +3991,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478932</v>
+        <v>478739</v>
       </c>
       <c r="R26" t="n">
-        <v>7027255</v>
+        <v>7027152</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3893,7 +4026,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3903,7 +4036,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>21:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor inom ca 6 m2 yta.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3917,7 +4055,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3935,48 +4073,62 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125814707</v>
+        <v>125814305</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>99142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478571</v>
+        <v>478668</v>
       </c>
       <c r="R27" t="n">
-        <v>7027142</v>
+        <v>7027201</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4005,7 +4157,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4015,7 +4167,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4029,27 +4181,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4067,38 +4199,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125813374</v>
+        <v>125815483</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>99142</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4107,13 +4253,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478958</v>
+        <v>478630</v>
       </c>
       <c r="R28" t="n">
-        <v>7027272</v>
+        <v>7027028</v>
       </c>
       <c r="S28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4142,7 +4288,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4152,7 +4298,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Två plantor mitt bland några guckusko-plantor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4166,27 +4317,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4204,48 +4335,68 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125813877</v>
+        <v>125832607</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>99142</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Albanobodarna, Albanobodarna, Jmt</t>
+          <t>Kvarnmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478823</v>
+        <v>478915</v>
       </c>
       <c r="R29" t="n">
-        <v>7027253</v>
+        <v>7027381</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4272,53 +4423,24 @@
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>21:01</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4336,10 +4458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125832601</v>
+        <v>125832700</v>
       </c>
       <c r="B30" t="n">
-        <v>98694</v>
+        <v>99142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4347,25 +4469,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>blomknopp</t>
@@ -4379,17 +4509,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Jmt</t>
+          <t>Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478915</v>
+        <v>478809</v>
       </c>
       <c r="R30" t="n">
-        <v>7027381</v>
+        <v>7027439</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4451,10 +4581,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125832607</v>
+        <v>125832601</v>
       </c>
       <c r="B31" t="n">
-        <v>98384</v>
+        <v>99456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4462,36 +4592,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>219880</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4574,43 +4696,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125812517</v>
+        <v>125811591</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4619,10 +4736,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478769</v>
+        <v>478763</v>
       </c>
       <c r="R32" t="n">
-        <v>7027240</v>
+        <v>7027381</v>
       </c>
       <c r="S32" t="n">
         <v>9</v>
@@ -4654,7 +4771,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4664,12 +4781,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en död gran som delvis är avbarkad troligen p.g.a födosökande tretåig hackspett.</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4683,27 +4795,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4721,10 +4813,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125832700</v>
+        <v>125811939</v>
       </c>
       <c r="B33" t="n">
-        <v>98384</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4732,57 +4824,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Albanobodarna, Jmt</t>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478809</v>
+        <v>478813</v>
       </c>
       <c r="R33" t="n">
-        <v>7027439</v>
+        <v>7027365</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4809,24 +4886,33 @@
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-06-08</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4844,10 +4930,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125815143</v>
+        <v>125812706</v>
       </c>
       <c r="B34" t="n">
-        <v>98267</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4855,36 +4941,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>504</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4893,10 +4970,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478555</v>
+        <v>478787</v>
       </c>
       <c r="R34" t="n">
-        <v>7027087</v>
+        <v>7027200</v>
       </c>
       <c r="S34" t="n">
         <v>8</v>
@@ -4928,7 +5005,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4938,12 +5015,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>21:39</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Minst 36 plantor inom ca 1 m2 yta.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4957,7 +5029,7 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4972,6 +5044,474 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125813227</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>478932</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7027255</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:39</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125813534</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>478904</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7027279</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125814202</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>478726</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7027177</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>21:14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125814512</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Albanobodarna, Albanobodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>478607</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7027167</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21932-2025 artfynd.xlsx
+++ b/artfynd/A 21932-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -803,6 +808,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125815143</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -939,6 +949,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125815433</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125810800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1208,6 +1228,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811759</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1340,6 +1365,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813564</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1472,6 +1502,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813877</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1604,6 +1639,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814707</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1741,6 +1781,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812909</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1883,6 +1928,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812974</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2020,6 +2070,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813002</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2157,6 +2212,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813374</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2294,6 +2354,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813307</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2436,6 +2501,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812928</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2578,6 +2648,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813824</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2725,6 +2800,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812517</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2872,6 +2952,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812647</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3019,6 +3104,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813429</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3161,6 +3251,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814666</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3303,6 +3398,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814842</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3429,6 +3529,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132795678</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3560,6 +3665,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811849</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3691,6 +3801,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814170</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3822,6 +3937,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811550</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3939,6 +4059,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811877</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4070,6 +4195,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814085</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4196,6 +4326,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814305</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4332,6 +4467,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125815483</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4455,6 +4595,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832607</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4578,6 +4723,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832700</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4693,6 +4843,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125832601</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4810,6 +4965,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811591</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4927,6 +5087,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125811939</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5044,6 +5209,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125812706</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5161,6 +5331,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813227</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5278,6 +5453,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125813534</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5395,6 +5575,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814202</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5512,8 +5697,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125814512</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>